--- a/important_mails_2026-03-21.xlsx
+++ b/important_mails_2026-03-21.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,86 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
+          <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Reminder: Please share your feedback on MCF</t>
+          <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家：
+						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
+						每年 4-7 月欧美迎来学期末大促，紧接着7-10月进入返校季，在此期间学校批量采购教学设备，家庭为子女豪囤文具用品，企业为员工升级办公配置—— 千亿级市场需求在亚马逊集中爆发。根据亚马逊内部数据，相关ASIN转化率最高提升2.4倍。
+						为了帮助您把握这波商机，我们向您提前预告在这段时间内值得关注的选品方向，助您提前布局商品，做好库存准备。
+						哪些品类有机会爆发？
+						美国站
+						教室用品、书写工具及配件
+						纸张/笔记本、美术用品
+						家具、收纳与储物用品
+						笔记本电脑/平板/显示器
+						IT配件、餐饮服务用品
+						清洁用品与设备、玩具
+						欧洲站
+						办公用品、PC电脑
+						家居用品、家具
+						电子产品、厨房用品
+						商业/工业/科学用品
+						玩具、家居装修用品
+						以上仅为部分热门品类，您可结合店铺情况，重点关注与“教学办公、IT、家具与收纳、设施维护”相关的产品，点击下方文字了解具体商品推荐：
+						教学办公
+https://go.amazonsellerservices.com/e/229492/pageName-CN3AAS3AGS-B2B3Aintro/7z264nh/6566697502/h/Mt_Wi0H4RcCqjfEopZWckMJLYMWHT-V0a58wxKYZDFY
+						商用 IT
+https://go.amazonsellerservices.com/e/229492/pageName-CN3AAS3AGS-B2B3Aintro/7z264nl/6566697502/h/Mt_Wi0H4RcCqjfEopZWckMJLYMWHT-V0a58wxKYZDFY
+						家具与收纳
+https://go.amazonsellerservices.com/e/229492/pageName-CN3AAS3AGS-B2B3Aintro/7z264np/6566697502/h/Mt_Wi0H4RcCqjfEopZWckMJLYMWHT-V0a58wxKYZDFY
+						设施维护
+https://go.amazonsellerservices.com/e/229492/pageName-CN3AAS3AGS-B2B3Aintro/7z264ns/6566697502/h/Mt_Wi0H4RcCqjfEopZWckMJLYMWHT-V0a58wxKYZDFY
+						亚马逊店铺商品默认 C+B 双端同步可售，您的商品能够同时展现给个人消费者和</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Please share your feedback on MCF</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -528,39 +593,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -577,39 +642,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -625,39 +690,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -676,39 +741,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -724,39 +789,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -772,39 +837,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -822,39 +887,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -871,39 +936,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -927,39 +992,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -974,39 +1039,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -1022,39 +1087,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1071,40 +1136,40 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1120,39 +1185,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1173,39 +1238,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1229,39 +1294,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1284,40 +1349,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1336,40 +1401,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1387,40 +1452,40 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1436,39 +1501,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1488,39 +1553,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1534,39 +1599,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1586,39 +1651,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1639,39 +1704,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1691,39 +1756,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1743,40 +1808,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -1792,39 +1857,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1850,39 +1915,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1903,39 +1968,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 21:45:54 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (SOu11lTFx5)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1961,39 +2026,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 03:59:48 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2009,39 +2074,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2056,39 +2121,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2112,39 +2177,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2158,39 +2223,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2207,39 +2272,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2259,39 +2324,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2308,39 +2373,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2364,39 +2429,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2416,39 +2481,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2468,39 +2533,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 14:54:33 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2516,39 +2581,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:38:32 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2568,39 +2633,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:37:02 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2620,39 +2685,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 15:49:30 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europa &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Ajuste de saldo negativo en tus cuentas de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2676,39 +2741,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 12:00:21 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2728,39 +2793,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2778,39 +2843,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2832,39 +2897,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2887,39 +2952,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2938,39 +3003,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2989,39 +3054,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3041,39 +3106,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3093,39 +3158,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3143,39 +3208,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3193,39 +3258,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3243,39 +3308,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3294,39 +3359,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3344,40 +3409,40 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3395,39 +3460,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3445,39 +3510,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3495,39 +3560,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3542,39 +3607,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3590,39 +3655,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3640,39 +3705,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3690,39 +3755,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3740,40 +3805,40 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3792,39 +3857,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3842,39 +3907,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3896,39 +3961,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3946,39 +4011,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3997,39 +4062,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4048,39 +4113,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento para los listados</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 Acción requerida: Información importante sobre tus listados de productos
@@ -4097,39 +4162,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Wed, 18 Feb 2026 20:09:07 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4148,39 +4213,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4200,39 +4265,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4248,40 +4313,40 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4297,39 +4362,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4346,39 +4411,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4397,39 +4462,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4447,39 +4512,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4491,39 +4556,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4535,39 +4600,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4579,39 +4644,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4623,39 +4688,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4667,39 +4732,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4711,39 +4776,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4755,39 +4820,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4799,39 +4864,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -4849,39 +4914,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -4924,39 +4989,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4973,40 +5038,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5024,39 +5089,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5074,39 +5139,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5118,39 +5183,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5162,39 +5227,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5213,39 +5278,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5257,39 +5322,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5301,39 +5366,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5345,39 +5410,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5389,39 +5454,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5433,39 +5498,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5477,39 +5542,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5521,39 +5586,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5565,39 +5630,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5609,40 +5674,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5661,39 +5726,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5705,40 +5770,40 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5750,39 +5815,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5794,39 +5859,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5845,39 +5910,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5889,39 +5954,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5940,39 +6005,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -5984,39 +6049,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6032,40 +6097,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6083,39 +6148,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6133,39 +6198,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6181,39 +6246,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6231,39 +6296,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6304,39 +6369,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6354,40 +6419,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6405,39 +6470,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6454,39 +6519,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6504,39 +6569,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6554,39 +6619,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6601,39 +6666,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6647,39 +6712,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6695,39 +6760,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6743,39 +6808,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6792,40 +6857,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6841,39 +6906,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -6902,39 +6967,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6951,40 +7016,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7001,39 +7066,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7048,40 +7113,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7096,39 +7161,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7143,39 +7208,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7190,39 +7255,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7237,39 +7302,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7297,39 +7362,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
@@ -7343,39 +7408,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 04:17:16 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7394,39 +7459,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7449,39 +7514,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7503,39 +7568,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7558,39 +7623,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7613,39 +7678,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7671,39 +7736,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7725,39 +7790,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7781,39 +7846,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -7825,39 +7890,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:43:58 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7881,39 +7946,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:32:50 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-05</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7934,39 +7999,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7980,39 +8045,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8030,39 +8095,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8079,39 +8144,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8129,40 +8194,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8181,39 +8246,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8229,39 +8294,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8291,40 +8356,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8343,40 +8408,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8394,39 +8459,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.

--- a/important_mails_2026-03-21.xlsx
+++ b/important_mails_2026-03-21.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>店铺绩效类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,124 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
+          <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID pVfzD86piw
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on April 5, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-1213863031250684</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -547,39 +650,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -593,39 +696,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -642,39 +745,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -690,90 +793,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/12/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FCDRNTT8
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-1917550476493542</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -789,39 +841,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -837,39 +889,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -887,39 +939,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -936,39 +988,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -992,39 +1044,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1039,39 +1091,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -1087,39 +1139,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1136,40 +1188,40 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1185,39 +1237,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1238,39 +1290,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1294,39 +1346,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1349,40 +1401,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1401,40 +1453,40 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1452,40 +1504,40 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1501,39 +1553,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1553,39 +1605,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1599,39 +1651,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1651,39 +1703,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1704,39 +1756,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1756,39 +1808,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1808,40 +1860,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -1857,39 +1909,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1915,39 +1967,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1968,39 +2020,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Feb 2026 21:45:54 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (SOu11lTFx5)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2026,54 +2078,6 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Feb 2026 03:59:48 +0000</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -2688,7 +2692,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2703,48 +2707,43 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:49:30 +0000</t>
+          <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Amazon Payments Europa &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Ajuste de saldo negativo en tus cuentas de Vender en Amazon</t>
+          <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>96
-This title will display on mobile devices
- Hemos ajustado tu saldo negativo de €3.55 que se adeudaba de tu cuenta de vendedor Amazon.es en febrero 19, 2026, con fondos que estaban disponibles en tu cuenta Amazon.fr. Puedes ver el saldo de tu cuenta en cualquier momento accediendo a tu cuenta y navegando hasta el panel de control Pagos .
-Para más información, consulta la sección Ajuste de saldo negativo en tus cuentas .
-Atentamente,
-Amazon Payments Europa
- Informar de un problema con este correo electrónico
- Si tienes alguna pregunta, consulta: Seller Central
- Para modificar tus preferencias de correo electrónico, consulta: Preferencias de notificación
- Copyright 2026 Amazon, Inc. o sus filiales. Todos los derechos reservados.
- Amazon Payments Europe
- 38 avenue John F. Kennedy,
- L-1855 Luxemburgo,
- Número de Registro en Luxemburgo: No. B-101818,
- Capital Social 165.833 EUR,
- Número de licencia de actividad: 134248,
- Nº de Registro IVA en Luxemburgo: LU 20260743.
- Este mensaje se envía desde una dirección de correo electrónico sin supervisión.
- SPC-EUAmazon-1776812415580202</t>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/12/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FCDRNTT8
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-1917550476493542</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2759,7 +2758,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 12:00:21 +0000</t>
+          <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2769,63 +2768,11 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
-On 02/19/26 12:00 PST, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
- 219.30.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
- Amazon sellers and Amazon Pay merchants can si</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2843,39 +2790,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2897,39 +2844,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2952,39 +2899,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3003,39 +2950,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3054,39 +3001,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3106,39 +3053,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3158,39 +3105,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3208,39 +3155,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3258,39 +3205,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3308,39 +3255,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3359,39 +3306,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3409,40 +3356,40 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3460,39 +3407,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3510,39 +3457,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3560,39 +3507,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3607,39 +3554,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3655,39 +3602,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3705,39 +3652,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3755,39 +3702,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3805,40 +3752,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3857,39 +3804,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3907,39 +3854,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3961,39 +3908,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -4011,39 +3958,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4062,39 +4009,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4113,39 +4060,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento para los listados</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 Acción requerida: Información importante sobre tus listados de productos
@@ -4162,90 +4109,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 18 Feb 2026 20:09:07 +0000</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4265,39 +4161,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4313,40 +4209,40 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4362,39 +4258,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4411,39 +4307,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4462,39 +4358,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4512,39 +4408,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4556,39 +4452,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4600,39 +4496,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4644,39 +4540,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4688,39 +4584,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4732,39 +4628,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4776,39 +4672,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4820,39 +4716,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4864,39 +4760,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -4914,39 +4810,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -4989,39 +4885,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5038,40 +4934,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5089,39 +4985,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5139,39 +5035,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5183,39 +5079,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5227,39 +5123,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5278,39 +5174,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5322,39 +5218,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5366,39 +5262,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5410,39 +5306,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5454,39 +5350,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5498,39 +5394,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5542,39 +5438,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5586,39 +5482,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5630,39 +5526,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5674,40 +5570,40 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5726,39 +5622,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5770,40 +5666,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5815,39 +5711,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5859,39 +5755,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5910,39 +5806,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5954,39 +5850,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6005,39 +5901,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6049,39 +5945,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6097,40 +5993,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6148,39 +6044,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6198,39 +6094,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6246,39 +6142,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6296,39 +6192,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6369,39 +6265,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6419,40 +6315,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6470,39 +6366,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6519,39 +6415,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6569,39 +6465,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6619,39 +6515,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6666,39 +6562,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6712,39 +6608,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6760,39 +6656,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6808,39 +6704,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6857,40 +6753,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6906,39 +6802,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -6967,39 +6863,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7016,40 +6912,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7066,39 +6962,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7113,40 +7009,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7161,39 +7057,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7208,39 +7104,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7255,39 +7151,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7302,39 +7198,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7362,39 +7258,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
@@ -7408,90 +7304,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Feb 2026 04:17:16 +0000</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Act today &amp; improve Sales on Excess Inventory</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Optional preview text
- Hello,
-We noticed you have a number of ASIN(s) that have excess levels of inventory. We are reaching out to inform you about multiple options to improve your Unit Sales on your aged and/or excess inventory in Amazon Fulfillment Centers. Our goal is to help you increase the sales on this excess inventory:
-X004QEYPRL, X004MMFUYT, X004QEVV05
-We encourage you to take Amazon recommended actions such as Create Outlet deals, Sponsor Products Ad, to improve sell through of this excess inventory and potentially reduce your chances of incurring aged inventory fee.
- Outlet deals
- Amazon Outlet is a great place for customers to shop for overstock deals, which offers a selection of items, such as electronics, toys, beauty, and kitchen.
- Create Outlet Deal Today!
- Sponsored Product Ads
- Sponsored Products is a cost-per-click advertising solution that provides advertisers with a foundation of controls and visibility to help get their individual products discovered, and help generate sales from traffic sources in the Amazon store and on select premium apps and websites.
- Create Sponsored Products Ad Today!
-We encourage you to vie</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7514,39 +7359,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7568,39 +7413,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7623,39 +7468,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7678,39 +7523,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7736,39 +7581,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7790,39 +7635,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7846,39 +7691,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -7890,39 +7735,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:43:58 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7946,39 +7791,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Feb 2026 13:32:50 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-05</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7999,39 +7844,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -8045,39 +7890,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8095,39 +7940,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8144,39 +7989,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8194,40 +8039,40 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8246,39 +8091,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8294,39 +8139,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8356,40 +8201,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8408,40 +8253,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8459,39 +8304,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.
